--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123187757</v>
+        <v>123185863</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628138</v>
+        <v>628232</v>
       </c>
       <c r="R2" t="n">
-        <v>6896290</v>
+        <v>6896392</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123185863</v>
+        <v>123187757</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628232</v>
+        <v>628138</v>
       </c>
       <c r="R3" t="n">
-        <v>6896392</v>
+        <v>6896290</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191792</v>
+        <v>123211050</v>
       </c>
       <c r="B4" t="n">
         <v>90952</v>
@@ -938,16 +938,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627930</v>
+        <v>628144</v>
       </c>
       <c r="R4" t="n">
-        <v>6896631</v>
+        <v>6896298</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,19 +980,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123211050</v>
+        <v>123191792</v>
       </c>
       <c r="B5" t="n">
         <v>90952</v>
@@ -1050,19 +1044,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628144</v>
+        <v>627930</v>
       </c>
       <c r="R5" t="n">
-        <v>6896298</v>
+        <v>6896631</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,9 +1083,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B2" t="n">
         <v>90952</v>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R2" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +751,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123187757</v>
+        <v>123185863</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628138</v>
+        <v>628232</v>
       </c>
       <c r="R3" t="n">
-        <v>6896290</v>
+        <v>6896392</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123211050</v>
+        <v>123191792</v>
       </c>
       <c r="B4" t="n">
         <v>90952</v>
@@ -938,19 +927,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628144</v>
+        <v>627930</v>
       </c>
       <c r="R4" t="n">
-        <v>6896298</v>
+        <v>6896631</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -980,9 +966,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123191792</v>
+        <v>123187757</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627930</v>
+        <v>628138</v>
       </c>
       <c r="R5" t="n">
-        <v>6896631</v>
+        <v>6896290</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123211050</v>
+        <v>123191792</v>
       </c>
       <c r="B2" t="n">
         <v>90952</v>
@@ -709,19 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628144</v>
+        <v>627930</v>
       </c>
       <c r="R2" t="n">
-        <v>6896298</v>
+        <v>6896631</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,9 +748,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B3" t="n">
         <v>90952</v>
@@ -815,16 +821,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R3" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,19 +863,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191792</v>
+        <v>123187757</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,34 +909,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627930</v>
+        <v>628138</v>
       </c>
       <c r="R4" t="n">
-        <v>6896631</v>
+        <v>6896290</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123187757</v>
+        <v>123185863</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,39 +1026,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628138</v>
+        <v>628232</v>
       </c>
       <c r="R5" t="n">
-        <v>6896290</v>
+        <v>6896392</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123191792</v>
+        <v>123187757</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627930</v>
+        <v>628138</v>
       </c>
       <c r="R2" t="n">
-        <v>6896631</v>
+        <v>6896290</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123211050</v>
+        <v>123185863</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,19 +826,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628144</v>
+        <v>628232</v>
       </c>
       <c r="R3" t="n">
-        <v>6896298</v>
+        <v>6896392</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,9 +865,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123187757</v>
+        <v>123191792</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628138</v>
+        <v>627930</v>
       </c>
       <c r="R4" t="n">
-        <v>6896290</v>
+        <v>6896631</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1050,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R5" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,19 +1092,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123187757</v>
+        <v>123211050</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628138</v>
+        <v>628144</v>
       </c>
       <c r="R2" t="n">
-        <v>6896290</v>
+        <v>6896298</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,19 +751,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,7 +784,7 @@
         <v>123185863</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -904,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123191792</v>
+        <v>123187757</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +909,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>627930</v>
+        <v>628138</v>
       </c>
       <c r="R4" t="n">
-        <v>6896631</v>
+        <v>6896290</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123211050</v>
+        <v>123191792</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,19 +1044,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628144</v>
+        <v>627930</v>
       </c>
       <c r="R5" t="n">
-        <v>6896298</v>
+        <v>6896631</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,9 +1083,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123211050</v>
+        <v>123185863</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,19 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628144</v>
+        <v>628232</v>
       </c>
       <c r="R2" t="n">
-        <v>6896298</v>
+        <v>6896392</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,9 +748,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +821,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R3" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,19 +863,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>123191792</v>
       </c>
       <c r="B5" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,16 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R2" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +751,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123211050</v>
+        <v>123185863</v>
       </c>
       <c r="B3" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,19 +815,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628144</v>
+        <v>628232</v>
       </c>
       <c r="R3" t="n">
-        <v>6896298</v>
+        <v>6896392</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -863,9 +854,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>123191792</v>
       </c>
       <c r="B5" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123211050</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123185863</v>
+        <v>123191792</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628232</v>
+        <v>627930</v>
       </c>
       <c r="R3" t="n">
-        <v>6896392</v>
+        <v>6896631</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +896,7 @@
         <v>123187757</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123191792</v>
+        <v>123185863</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627930</v>
+        <v>628232</v>
       </c>
       <c r="R5" t="n">
-        <v>6896631</v>
+        <v>6896392</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123211050</v>
+        <v>123187757</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628144</v>
+        <v>628138</v>
       </c>
       <c r="R2" t="n">
-        <v>6896298</v>
+        <v>6896290</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,9 +753,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,7 +795,7 @@
         <v>123191792</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -893,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123187757</v>
+        <v>123185863</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628138</v>
+        <v>628232</v>
       </c>
       <c r="R4" t="n">
-        <v>6896290</v>
+        <v>6896392</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,16 +1050,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R5" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,19 +1092,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123187757</v>
+        <v>123191792</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628138</v>
+        <v>627930</v>
       </c>
       <c r="R2" t="n">
-        <v>6896290</v>
+        <v>6896631</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123191792</v>
+        <v>123185863</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>627930</v>
+        <v>628232</v>
       </c>
       <c r="R3" t="n">
-        <v>6896631</v>
+        <v>6896392</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,16 +933,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R4" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,19 +975,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,6 +986,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1016,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123211050</v>
+        <v>123187757</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628144</v>
+        <v>628138</v>
       </c>
       <c r="R5" t="n">
-        <v>6896298</v>
+        <v>6896290</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,9 +1083,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4871-2025 artfynd.xlsx
+++ b/artfynd/A 4871-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123191792</v>
+        <v>123185863</v>
       </c>
       <c r="B2" t="n">
         <v>90990</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>627930</v>
+        <v>628232</v>
       </c>
       <c r="R2" t="n">
-        <v>6896631</v>
+        <v>6896392</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123185863</v>
+        <v>123211050</v>
       </c>
       <c r="B3" t="n">
         <v>90990</v>
@@ -821,16 +821,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628232</v>
+        <v>628144</v>
       </c>
       <c r="R3" t="n">
-        <v>6896392</v>
+        <v>6896298</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +863,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123211050</v>
+        <v>123191792</v>
       </c>
       <c r="B4" t="n">
         <v>90990</v>
@@ -933,19 +927,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628144</v>
+        <v>627930</v>
       </c>
       <c r="R4" t="n">
-        <v>6896298</v>
+        <v>6896631</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -975,9 +966,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +987,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
